--- a/artfynd/A 25728-2024 artfynd.xlsx
+++ b/artfynd/A 25728-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1019,6 +1019,108 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120281070</v>
+      </c>
+      <c r="B5" t="n">
+        <v>89230</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1596</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Jättemusseron</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tricholoma colossus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skarsdalen, Dls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>341377</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6554650</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25728-2024 artfynd.xlsx
+++ b/artfynd/A 25728-2024 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>120281070</v>
       </c>
       <c r="B5" t="n">
-        <v>89230</v>
+        <v>89247</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 25728-2024 artfynd.xlsx
+++ b/artfynd/A 25728-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119219534</v>
+        <v>120281070</v>
       </c>
       <c r="B2" t="n">
-        <v>91183</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90674</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>1596</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Holmetjärnsåsen, Dls</t>
+          <t>Skarsdalen, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>341440</v>
+        <v>341377</v>
       </c>
       <c r="R2" t="n">
-        <v>6554717</v>
+        <v>6554650</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,55 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119219532</v>
+        <v>119219533</v>
       </c>
       <c r="B3" t="n">
-        <v>8430</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Holmetjärnsåsen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>341537</v>
+        <v>341545</v>
       </c>
       <c r="R3" t="n">
-        <v>6554810</v>
+        <v>6554760</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -868,21 +853,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119219535</v>
+        <v>119219534</v>
       </c>
       <c r="B4" t="n">
-        <v>5187</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,39 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>6031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Holmetjärnsåsen, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>341473</v>
+        <v>341440</v>
       </c>
       <c r="R4" t="n">
-        <v>6554697</v>
+        <v>6554717</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -990,21 +950,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1021,50 +966,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120281070</v>
+        <v>119219535</v>
       </c>
       <c r="B5" t="n">
-        <v>89297</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1596</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skarsdalen, Dls</t>
+          <t>Holmetjärnsåsen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>341377</v>
+        <v>341473</v>
       </c>
       <c r="R5" t="n">
-        <v>6554650</v>
+        <v>6554697</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1091,12 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,6 +1052,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1120,6 +1080,123 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119219532</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Holmetjärnsåsen, Dls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>341537</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6554810</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25728-2024 artfynd.xlsx
+++ b/artfynd/A 25728-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120281070</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119219533</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119219534</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119219535</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,8 +1222,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119219532</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>